--- a/dados/SURVEY_CBO.xlsx
+++ b/dados/SURVEY_CBO.xlsx
@@ -2792,7 +2792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22.5546875" customWidth="1" min="1" max="1"/>
@@ -3337,9 +3337,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.29930555556</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-21.949966</v>
       </c>
@@ -3349,10 +3346,32 @@
       <c r="Q20" s="21" t="n">
         <v>46232.03958333333</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-21.979753</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-39.765507</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>46234.64305555556</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -3369,7 +3388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="20.5546875" customWidth="1" min="1" max="1"/>
@@ -3914,9 +3933,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.29930555556</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-22.851622</v>
       </c>
@@ -3926,10 +3942,32 @@
       <c r="Q20" s="21" t="n">
         <v>46232.29722222222</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-23.254957</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-42.152786</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>46232.79652777778</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -3946,7 +3984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="29.109375" customWidth="1" min="1" max="1"/>
@@ -4485,9 +4523,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.30208333334</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-23.686735</v>
       </c>
@@ -4497,12 +4532,34 @@
       <c r="Q20" s="21" t="n">
         <v>46232.30069444444</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M21" t="n">
+        <v>-22.8944</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.201881</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>46234.65972222222</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.44140625" customWidth="1" min="1" max="1"/>
@@ -5050,9 +5107,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.30208333334</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-21.864763</v>
       </c>
@@ -5062,12 +5116,34 @@
       <c r="Q20" s="21" t="n">
         <v>46232.3</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Restricted Manoeuvrability</t>
+      <c r="M21" t="n">
+        <v>-22.835772</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.128948</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>46234.65833333333</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5622,9 +5698,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.30208333334</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-25.203926</v>
       </c>
@@ -5634,10 +5707,32 @@
       <c r="Q20" s="21" t="n">
         <v>46232.3</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-25.20393</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-42.877556</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>46232.60555555556</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -5654,7 +5749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="24.6640625" customWidth="1" min="1" max="1"/>
@@ -6190,9 +6285,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.30208333334</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-25.227072</v>
       </c>
@@ -6202,12 +6294,34 @@
       <c r="Q20" s="21" t="n">
         <v>46232.29930555556</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M21" t="n">
+        <v>-22.891062</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.213902</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="29.5546875" customWidth="1" min="1" max="1"/>
@@ -6771,9 +6885,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.30208333334</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-21.78054</v>
       </c>
@@ -6783,10 +6894,32 @@
       <c r="Q20" s="21" t="n">
         <v>46231.95555555556</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-21.829857</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-40.0867</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>46233.62013888889</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -6803,7 +6936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="24.109375" customWidth="1" min="1" max="1"/>
@@ -7336,9 +7469,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.30208333334</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-30.372272</v>
       </c>
@@ -7348,10 +7478,32 @@
       <c r="Q20" s="21" t="n">
         <v>44677.81111111111</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-30.372272</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-47.695133</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>44677.81111111111</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Class B</t>
         </is>
@@ -7368,7 +7520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -7905,9 +8057,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.30208333334</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-23.396547</v>
       </c>
@@ -7917,10 +8066,32 @@
       <c r="Q20" s="21" t="n">
         <v>46232.3</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-23.335497</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-41.314178</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>46233.05416666667</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -7937,7 +8108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -8470,9 +8641,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.30208333334</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-22.864527</v>
       </c>
@@ -8482,10 +8650,32 @@
       <c r="Q20" s="21" t="n">
         <v>45839.57638888889</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-22.864527</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.111076</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>45839.57638888889</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Moored</t>
         </is>
@@ -8502,7 +8692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="34.5546875" customWidth="1" min="1" max="1"/>
@@ -9038,9 +9228,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.29930555556</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-22.86651</v>
       </c>
@@ -9050,12 +9237,34 @@
       <c r="Q20" s="21" t="n">
         <v>46230.90625</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Moored</t>
+      <c r="M21" t="n">
+        <v>-22.842613</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.12973</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>46234.65347222222</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="24.88671875" customWidth="1" min="1" max="1"/>
@@ -9604,9 +9813,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.30208333334</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-24.369265</v>
       </c>
@@ -9616,12 +9822,34 @@
       <c r="Q20" s="21" t="n">
         <v>46232.30069444444</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M21" t="n">
+        <v>-24.652592</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-42.235107</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>46232.63888888889</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
     </row>
@@ -9636,7 +9864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="20.33203125" customWidth="1" min="1" max="1"/>
@@ -10175,9 +10403,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.30208333334</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-22.868595</v>
       </c>
@@ -10187,12 +10412,34 @@
       <c r="Q20" s="21" t="n">
         <v>46232.3</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.6625</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Moored</t>
+      <c r="M21" t="n">
+        <v>-25.491667</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.993332</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>46233.68263888889</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -10207,7 +10454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="28.109375" customWidth="1" min="1" max="1"/>
@@ -10743,9 +10990,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.30416666667</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-22.845821</v>
       </c>
@@ -10755,10 +10999,32 @@
       <c r="Q20" s="21" t="n">
         <v>46232.30208333334</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.65277777778</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-22.851479</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.139774</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>46234.64791666667</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -10775,7 +11041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="24.44140625" customWidth="1" min="1" max="1"/>
@@ -11316,9 +11582,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.30416666667</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-22.845169</v>
       </c>
@@ -11328,10 +11591,32 @@
       <c r="Q20" s="21" t="n">
         <v>46232.29375</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.65277777778</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-22.851097</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.144375</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>46234.64722222222</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -11348,7 +11633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="29.33203125" customWidth="1" min="1" max="1"/>
@@ -11886,9 +12171,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.29930555556</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-25.608391</v>
       </c>
@@ -11898,10 +12180,32 @@
       <c r="Q20" s="21" t="n">
         <v>46232.29583333333</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-25.617207</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-42.841625</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>46232.57638888889</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -11919,7 +12223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI32"/>
+  <dimension ref="A1:AI33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.5546875" customWidth="1" min="1" max="1"/>
@@ -13344,9 +13648,6 @@
       <c r="A32" s="21" t="n">
         <v>46232.29930555556</v>
       </c>
-      <c r="B32" t="n">
-        <v/>
-      </c>
       <c r="M32" t="n">
         <v>-23.542109</v>
       </c>
@@ -13356,10 +13657,32 @@
       <c r="Q32" s="21" t="n">
         <v>46232.29652777778</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B33" t="n">
         <v/>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="M33" t="n">
+        <v>-23.205189</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-42.382423</v>
+      </c>
+      <c r="Q33" s="21" t="n">
+        <v>46234.21458333333</v>
+      </c>
+      <c r="R33" t="n">
+        <v/>
+      </c>
+      <c r="S33" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -13377,7 +13700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="28.5546875" customWidth="1" min="1" max="1"/>
@@ -15536,9 +15859,6 @@
       <c r="A44" s="21" t="n">
         <v>46232.29930555556</v>
       </c>
-      <c r="B44" t="n">
-        <v/>
-      </c>
       <c r="M44" t="n">
         <v>-24.625259</v>
       </c>
@@ -15548,12 +15868,34 @@
       <c r="Q44" s="21" t="n">
         <v>46232.12222222222</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B45" t="n">
         <v/>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M45" t="n">
+        <v>-22.881655</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-43.117458</v>
+      </c>
+      <c r="Q45" s="21" t="n">
+        <v>46234.65069444444</v>
+      </c>
+      <c r="R45" t="n">
+        <v/>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
@@ -15568,7 +15910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="33.44140625" customWidth="1" min="1" max="1"/>
@@ -16105,9 +16447,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.29930555556</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-22.864473</v>
       </c>
@@ -16117,10 +16456,32 @@
       <c r="Q20" s="21" t="n">
         <v>44390.56527777778</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-22.864473</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.109585</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>44390.56527777778</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Moored</t>
         </is>
@@ -16137,7 +16498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="38.77734375" customWidth="1" min="1" max="1"/>
@@ -16676,9 +17037,6 @@
       <c r="A20" s="21" t="n">
         <v>46232.29930555556</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-24.681929</v>
       </c>
@@ -16688,12 +17046,34 @@
       <c r="Q20" s="21" t="n">
         <v>46232.29444444444</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Restricted Manoeuvrability</t>
+      <c r="M21" t="n">
+        <v>-22.848303</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.133507</v>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>46234.65277777778</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
         </is>
       </c>
     </row>
@@ -16708,7 +17088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22.21875" customWidth="1" min="1" max="1"/>
@@ -17454,9 +17834,6 @@
       <c r="A22" s="21" t="n">
         <v>46232.29930555556</v>
       </c>
-      <c r="B22" t="n">
-        <v/>
-      </c>
       <c r="M22" t="n">
         <v>-24.532534</v>
       </c>
@@ -17466,12 +17843,34 @@
       <c r="Q22" s="21" t="n">
         <v>46232.28888888889</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Restricted Manoeuvrability</t>
+      <c r="M23" t="n">
+        <v>-23.272249</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-42.995266</v>
+      </c>
+      <c r="Q23" s="21" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -17493,7 +17892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18062,9 +18461,6 @@
       <c r="A21" s="21" t="n">
         <v>46232.29930555556</v>
       </c>
-      <c r="B21" t="n">
-        <v/>
-      </c>
       <c r="M21" t="n">
         <v>-25.514156</v>
       </c>
@@ -18074,12 +18470,34 @@
       <c r="Q21" s="21" t="n">
         <v>46232.28888888889</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46234.65902777778</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Restricted Manoeuvrability</t>
+      <c r="M22" t="n">
+        <v>-22.867237</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-43.205769</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>

--- a/dados/SURVEY_CBO.xlsx
+++ b/dados/SURVEY_CBO.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="988" firstSheet="13" activeTab="15" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="988" firstSheet="9" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posicoes" sheetId="1" state="visible" r:id="rId1"/>
@@ -558,9 +558,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G93"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25.44140625" customWidth="1" min="1" max="7"/>
+    <col width="25.42578125" customWidth="1" min="1" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -909,7 +909,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>TIDAL ACTION(Navio Sonda)</t>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>PETROBRAS 62 (P-62)(FPSO)</t>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="28.8" customHeight="1">
+    <row r="82" ht="28.9" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
         <is>
           <t>FPSO MARECHAL DUQUE DE CAXIAS</t>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="28.8" customHeight="1">
+    <row r="91" ht="28.9" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
           <t>VERMELHO 1 (PVM-1)Fixa (Habitada)</t>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="28.8" customHeight="1">
+    <row r="92" ht="28.9" customHeight="1">
       <c r="A92" s="8" t="inlineStr">
         <is>
           <t>VERMELHO 3 (PVM-3)Fixa (Desabitada)</t>
@@ -2792,24 +2792,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22.5546875" customWidth="1" min="1" max="1"/>
-    <col width="7.77734375" customWidth="1" min="2" max="2"/>
-    <col width="9.109375" customWidth="1" style="4" min="3" max="3"/>
-    <col width="6.44140625" customWidth="1" min="4" max="4"/>
-    <col width="7.109375" customWidth="1" min="7" max="7"/>
-    <col width="9.109375" customWidth="1" style="3" min="8" max="8"/>
-    <col width="8.88671875" customWidth="1" min="9" max="9"/>
-    <col width="10.5546875" customWidth="1" min="11" max="11"/>
-    <col width="7.77734375" customWidth="1" min="12" max="12"/>
-    <col width="13.5546875" customWidth="1" min="13" max="14"/>
-    <col width="10.6640625" customWidth="1" min="15" max="15"/>
-    <col width="7.44140625" customWidth="1" min="16" max="16"/>
-    <col width="14.44140625" customWidth="1" min="17" max="17"/>
-    <col width="16.33203125" customWidth="1" min="18" max="18"/>
-    <col width="33.77734375" customWidth="1" min="19" max="19"/>
+    <col width="22.5703125" customWidth="1" min="1" max="1"/>
+    <col width="7.7109375" customWidth="1" min="2" max="2"/>
+    <col width="9.140625" customWidth="1" style="4" min="3" max="3"/>
+    <col width="6.42578125" customWidth="1" min="4" max="4"/>
+    <col width="7.140625" customWidth="1" min="7" max="7"/>
+    <col width="9.140625" customWidth="1" style="3" min="8" max="8"/>
+    <col width="8.85546875" customWidth="1" min="9" max="9"/>
+    <col width="10.5703125" customWidth="1" min="11" max="11"/>
+    <col width="7.7109375" customWidth="1" min="12" max="12"/>
+    <col width="13.5703125" customWidth="1" min="13" max="14"/>
+    <col width="10.7109375" customWidth="1" min="15" max="15"/>
+    <col width="7.42578125" customWidth="1" min="16" max="16"/>
+    <col width="14.42578125" customWidth="1" min="17" max="17"/>
+    <col width="16.28515625" customWidth="1" min="18" max="18"/>
+    <col width="33.7109375" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2920,7 +2920,7 @@
         <v>-21.88</v>
       </c>
       <c r="N2" t="n">
-        <v>41.01</v>
+        <v>-41.01</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -3334,7 +3334,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.29930555556</v>
       </c>
       <c r="M20" t="n">
@@ -3343,7 +3343,7 @@
       <c r="N20" t="n">
         <v>-39.713375</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>46232.03958333333</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -3353,11 +3353,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.65902777778</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-21.979753</v>
@@ -3365,13 +3362,35 @@
       <c r="N21" t="n">
         <v>-39.765507</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46234.64305555556</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-21.978468</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-39.766022</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>46235.17708333334</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -3388,24 +3407,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="13.6640625" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="13.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="20.5546875" customWidth="1" min="1" max="1"/>
-    <col width="13.88671875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="7.44140625" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="13.5546875" customWidth="1" min="4" max="4"/>
-    <col width="7.109375" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="10.6640625" bestFit="1" customWidth="1" min="6" max="7"/>
-    <col width="13.109375" customWidth="1" style="4" min="8" max="8"/>
+    <col width="20.5703125" customWidth="1" min="1" max="1"/>
+    <col width="13.85546875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="7.42578125" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="13.5703125" customWidth="1" min="4" max="4"/>
+    <col width="7.140625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" min="6" max="7"/>
+    <col width="13.140625" customWidth="1" style="4" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="7" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="10.6640625" bestFit="1" customWidth="1" min="11" max="14"/>
-    <col width="5.109375" customWidth="1" min="15" max="15"/>
-    <col width="6.21875" customWidth="1" min="16" max="16"/>
-    <col width="14.6640625" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="6.88671875" customWidth="1" min="18" max="18"/>
-    <col width="28.109375" customWidth="1" min="19" max="19"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" min="11" max="14"/>
+    <col width="5.140625" customWidth="1" min="15" max="15"/>
+    <col width="6.28515625" customWidth="1" min="16" max="16"/>
+    <col width="14.7109375" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="6.85546875" customWidth="1" min="18" max="18"/>
+    <col width="28.140625" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3930,7 +3949,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.29930555556</v>
       </c>
       <c r="M20" t="n">
@@ -3939,7 +3958,7 @@
       <c r="N20" t="n">
         <v>-43.135208</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>46232.29722222222</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -3949,11 +3968,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.65902777778</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-23.254957</v>
@@ -3961,15 +3977,37 @@
       <c r="N21" t="n">
         <v>-42.152786</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46232.79652777778</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M22" t="n">
+        <v>-23.563128</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-41.130524</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>46235.11458333334</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -3984,18 +4022,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29.109375" customWidth="1" min="1" max="1"/>
-    <col width="2.5546875" customWidth="1" min="3" max="3"/>
-    <col width="3.6640625" customWidth="1" min="4" max="4"/>
-    <col width="2.33203125" customWidth="1" min="5" max="5"/>
-    <col width="2.6640625" customWidth="1" min="6" max="6"/>
-    <col width="3.33203125" customWidth="1" min="7" max="7"/>
-    <col width="3.44140625" customWidth="1" min="8" max="8"/>
-    <col width="11.21875" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="27.77734375" customWidth="1" min="19" max="19"/>
+    <col width="29.140625" customWidth="1" min="1" max="1"/>
+    <col width="2.5703125" customWidth="1" min="3" max="3"/>
+    <col width="3.7109375" customWidth="1" min="4" max="4"/>
+    <col width="2.28515625" customWidth="1" min="5" max="5"/>
+    <col width="2.7109375" customWidth="1" min="6" max="6"/>
+    <col width="3.28515625" customWidth="1" min="7" max="7"/>
+    <col width="3.42578125" customWidth="1" min="8" max="8"/>
+    <col width="11.28515625" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="27.7109375" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4520,7 +4558,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.30208333334</v>
       </c>
       <c r="M20" t="n">
@@ -4529,7 +4567,7 @@
       <c r="N20" t="n">
         <v>-42.879116</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>46232.30069444444</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -4539,11 +4577,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.6625</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-22.8944</v>
@@ -4551,13 +4586,35 @@
       <c r="N21" t="n">
         <v>-43.201881</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46234.65972222222</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-22.894381</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-43.201912</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>46235.41319444445</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Moored</t>
         </is>
@@ -4574,11 +4631,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.44140625" customWidth="1" min="1" max="1"/>
-    <col width="11.21875" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="23.42578125" customWidth="1" min="1" max="1"/>
+    <col width="11.28515625" bestFit="1" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -5104,7 +5161,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.30208333334</v>
       </c>
       <c r="M20" t="n">
@@ -5113,7 +5170,7 @@
       <c r="N20" t="n">
         <v>-41.016373</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>46232.3</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -5123,11 +5180,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.6625</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-22.835772</v>
@@ -5135,13 +5189,35 @@
       <c r="N21" t="n">
         <v>-43.128948</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46234.65833333333</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-22.836294</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-43.128826</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>46235.41666666666</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -5158,19 +5234,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="4" customWidth="1" min="4" max="4"/>
     <col width="3" customWidth="1" min="5" max="5"/>
-    <col width="3.33203125" customWidth="1" min="6" max="6"/>
-    <col width="4.109375" customWidth="1" min="7" max="7"/>
-    <col width="3.77734375" customWidth="1" min="8" max="8"/>
-    <col width="14.6640625" customWidth="1" min="9" max="9"/>
-    <col width="11.5546875" customWidth="1" min="12" max="12"/>
-    <col width="13.5546875" customWidth="1" min="17" max="17"/>
-    <col width="27.109375" customWidth="1" min="19" max="19"/>
+    <col width="3.28515625" customWidth="1" min="6" max="6"/>
+    <col width="4.140625" customWidth="1" min="7" max="7"/>
+    <col width="3.7109375" customWidth="1" min="8" max="8"/>
+    <col width="14.7109375" customWidth="1" min="9" max="9"/>
+    <col width="11.5703125" customWidth="1" min="12" max="12"/>
+    <col width="13.5703125" customWidth="1" min="17" max="17"/>
+    <col width="27.140625" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5695,7 +5771,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.30208333334</v>
       </c>
       <c r="M20" t="n">
@@ -5704,7 +5780,7 @@
       <c r="N20" t="n">
         <v>-42.877399</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>46232.3</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -5714,11 +5790,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.6625</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-25.20393</v>
@@ -5726,13 +5799,35 @@
       <c r="N21" t="n">
         <v>-42.877556</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46232.60555555556</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-25.20393</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-42.877556</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>46232.60555555556</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -5749,15 +5844,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24.6640625" customWidth="1" min="1" max="1"/>
+    <col width="24.7109375" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="5.77734375" customWidth="1" min="6" max="6"/>
-    <col width="6.88671875" customWidth="1" min="7" max="7"/>
-    <col width="10.44140625" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="28.109375" customWidth="1" min="19" max="19"/>
+    <col width="5.7109375" customWidth="1" min="6" max="6"/>
+    <col width="6.85546875" customWidth="1" min="7" max="7"/>
+    <col width="10.42578125" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="28.140625" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6282,7 +6377,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.30208333334</v>
       </c>
       <c r="M20" t="n">
@@ -6291,7 +6386,7 @@
       <c r="N20" t="n">
         <v>-42.570938</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>46232.29930555556</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -6301,11 +6396,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.6625</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-22.891062</v>
@@ -6313,13 +6405,35 @@
       <c r="N21" t="n">
         <v>-43.213902</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46234.65902777778</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-22.895193</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-43.203777</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>46235.41666666666</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -6336,28 +6450,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29.5546875" customWidth="1" min="1" max="1"/>
-    <col width="14.44140625" customWidth="1" min="2" max="2"/>
-    <col width="7.44140625" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
-    <col width="6.109375" customWidth="1" min="4" max="4"/>
-    <col width="7.109375" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="10.6640625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="7.5546875" customWidth="1" min="7" max="7"/>
-    <col width="12.21875" customWidth="1" style="3" min="8" max="8"/>
-    <col width="7.33203125" customWidth="1" min="9" max="9"/>
-    <col width="5.109375" customWidth="1" min="10" max="10"/>
-    <col width="9.6640625" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="10.6640625" bestFit="1" customWidth="1" min="12" max="12"/>
-    <col width="11.21875" customWidth="1" min="13" max="13"/>
-    <col width="10.6640625" bestFit="1" customWidth="1" min="14" max="14"/>
-    <col width="6.6640625" customWidth="1" min="15" max="15"/>
-    <col width="5.6640625" bestFit="1" customWidth="1" min="16" max="16"/>
-    <col width="14.6640625" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="9.33203125" customWidth="1" min="18" max="18"/>
-    <col width="33.6640625" customWidth="1" min="19" max="19"/>
+    <col width="29.5703125" customWidth="1" min="1" max="1"/>
+    <col width="14.42578125" customWidth="1" min="2" max="2"/>
+    <col width="7.42578125" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
+    <col width="6.140625" customWidth="1" min="4" max="4"/>
+    <col width="7.140625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="7.5703125" customWidth="1" min="7" max="7"/>
+    <col width="12.28515625" customWidth="1" style="3" min="8" max="8"/>
+    <col width="7.28515625" customWidth="1" min="9" max="9"/>
+    <col width="5.140625" customWidth="1" min="10" max="10"/>
+    <col width="9.7109375" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="11.28515625" customWidth="1" min="13" max="13"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="6.7109375" customWidth="1" min="15" max="15"/>
+    <col width="5.7109375" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="14.7109375" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="9.28515625" customWidth="1" min="18" max="18"/>
+    <col width="33.7109375" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6882,7 +6996,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.30208333334</v>
       </c>
       <c r="M20" t="n">
@@ -6891,7 +7005,7 @@
       <c r="N20" t="n">
         <v>-39.785568</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>46231.95555555556</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -6901,11 +7015,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.6625</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-21.829857</v>
@@ -6913,15 +7024,37 @@
       <c r="N21" t="n">
         <v>-40.0867</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46233.62013888889</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M22" t="n">
+        <v>-21.214157</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-39.998188</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>46234.74513888889</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -6936,12 +7069,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24.109375" customWidth="1" min="1" max="1"/>
-    <col width="16.6640625" customWidth="1" min="17" max="17"/>
-    <col width="11.5546875" customWidth="1" min="19" max="19"/>
+    <col width="24.140625" customWidth="1" min="1" max="1"/>
+    <col width="16.7109375" customWidth="1" min="17" max="17"/>
+    <col width="11.5703125" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7466,7 +7599,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.30208333334</v>
       </c>
       <c r="M20" t="n">
@@ -7475,7 +7608,7 @@
       <c r="N20" t="n">
         <v>-47.695133</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>44677.81111111111</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -7485,11 +7618,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.6625</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-30.372272</v>
@@ -7497,13 +7627,35 @@
       <c r="N21" t="n">
         <v>-47.695133</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>44677.81111111111</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-30.372272</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-47.695133</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>44677.81111111111</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Class B</t>
         </is>
@@ -7520,16 +7672,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="3.33203125" customWidth="1" min="5" max="5"/>
-    <col width="2.88671875" customWidth="1" min="6" max="6"/>
-    <col width="3.33203125" customWidth="1" min="7" max="8"/>
-    <col width="2.6640625" customWidth="1" min="9" max="9"/>
-    <col width="11.21875" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="26.33203125" customWidth="1" min="19" max="19"/>
+    <col width="3.28515625" customWidth="1" min="5" max="5"/>
+    <col width="2.85546875" customWidth="1" min="6" max="6"/>
+    <col width="3.28515625" customWidth="1" min="7" max="8"/>
+    <col width="2.7109375" customWidth="1" min="9" max="9"/>
+    <col width="11.28515625" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="26.28515625" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8054,7 +8206,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.30208333334</v>
       </c>
       <c r="M20" t="n">
@@ -8063,7 +8215,7 @@
       <c r="N20" t="n">
         <v>-41.410007</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>46232.3</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -8073,11 +8225,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.6625</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-23.335497</v>
@@ -8085,13 +8234,35 @@
       <c r="N21" t="n">
         <v>-41.314178</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46233.05416666667</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-23.395836</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-41.408047</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>46235.17986111111</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -8108,12 +8279,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30.21875" customWidth="1" min="1" max="1"/>
-    <col width="21.109375" customWidth="1" min="17" max="17"/>
-    <col width="12.44140625" customWidth="1" min="19" max="19"/>
+    <col width="30.28515625" customWidth="1" min="1" max="1"/>
+    <col width="21.140625" customWidth="1" min="17" max="17"/>
+    <col width="12.42578125" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8638,7 +8809,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.30208333334</v>
       </c>
       <c r="M20" t="n">
@@ -8647,7 +8818,7 @@
       <c r="N20" t="n">
         <v>-43.111076</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>45839.57638888889</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -8657,11 +8828,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.6625</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-22.864527</v>
@@ -8669,13 +8837,35 @@
       <c r="N21" t="n">
         <v>-43.111076</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>45839.57638888889</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-22.864527</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-43.111076</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>45839.57638888889</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Moored</t>
         </is>
@@ -8692,14 +8882,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34.5546875" customWidth="1" min="1" max="1"/>
-    <col width="2.77734375" customWidth="1" min="7" max="7"/>
-    <col hidden="1" width="8.88671875" customWidth="1" min="8" max="12"/>
-    <col width="8.109375" customWidth="1" min="14" max="14"/>
-    <col width="21.33203125" customWidth="1" style="13" min="17" max="17"/>
+    <col width="34.5703125" customWidth="1" min="1" max="1"/>
+    <col width="2.7109375" customWidth="1" min="7" max="7"/>
+    <col hidden="1" width="8.85546875" customWidth="1" min="8" max="12"/>
+    <col width="8.140625" customWidth="1" min="14" max="14"/>
+    <col width="21.28515625" customWidth="1" style="13" min="17" max="17"/>
     <col width="17" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -9225,7 +9415,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.29930555556</v>
       </c>
       <c r="M20" t="n">
@@ -9234,7 +9424,7 @@
       <c r="N20" t="n">
         <v>-43.12978</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>46230.90625</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -9244,11 +9434,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.65902777778</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-22.842613</v>
@@ -9256,13 +9443,35 @@
       <c r="N21" t="n">
         <v>-43.12973</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46234.65347222222</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-22.843443</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-43.129742</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -9280,12 +9489,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24.88671875" customWidth="1" min="1" max="1"/>
-    <col width="10.44140625" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="29.77734375" customWidth="1" min="19" max="19"/>
+    <col width="24.85546875" customWidth="1" min="1" max="1"/>
+    <col width="10.42578125" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="29.7109375" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9810,7 +10019,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.30208333334</v>
       </c>
       <c r="M20" t="n">
@@ -9819,7 +10028,7 @@
       <c r="N20" t="n">
         <v>-42.394775</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>46232.30069444444</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -9829,11 +10038,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.6625</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-24.652592</v>
@@ -9841,13 +10047,35 @@
       <c r="N21" t="n">
         <v>-42.235107</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46232.63888888889</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-24.652592</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-42.235107</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>46232.63888888889</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -9864,18 +10092,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20.33203125" customWidth="1" min="1" max="1"/>
-    <col width="3.88671875" customWidth="1" min="5" max="5"/>
-    <col width="4.33203125" customWidth="1" min="6" max="6"/>
+    <col width="20.28515625" customWidth="1" min="1" max="1"/>
+    <col width="3.85546875" customWidth="1" min="5" max="5"/>
+    <col width="4.28515625" customWidth="1" min="6" max="6"/>
     <col width="3" customWidth="1" min="7" max="7"/>
-    <col width="2.6640625" customWidth="1" min="8" max="8"/>
-    <col width="2.21875" customWidth="1" min="9" max="9"/>
-    <col width="4.33203125" customWidth="1" min="10" max="10"/>
-    <col width="11.21875" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="29.33203125" customWidth="1" min="19" max="19"/>
+    <col width="2.7109375" customWidth="1" min="8" max="8"/>
+    <col width="2.28515625" customWidth="1" min="9" max="9"/>
+    <col width="4.28515625" customWidth="1" min="10" max="10"/>
+    <col width="11.28515625" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="29.28515625" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10400,7 +10628,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.30208333334</v>
       </c>
       <c r="M20" t="n">
@@ -10409,7 +10637,7 @@
       <c r="N20" t="n">
         <v>-43.211605</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>46232.3</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -10419,11 +10647,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.6625</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-25.491667</v>
@@ -10431,13 +10656,35 @@
       <c r="N21" t="n">
         <v>-43.993332</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46233.68263888889</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-25.491667</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-43.993332</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>46233.68263888889</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -10454,15 +10701,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28.109375" customWidth="1" min="1" max="1"/>
-    <col width="12.44140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="10.33203125" customWidth="1" min="8" max="8"/>
-    <col width="12.44140625" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="12.44140625" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="19.109375" customWidth="1" min="19" max="19"/>
+    <col width="28.140625" customWidth="1" min="1" max="1"/>
+    <col width="12.42578125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="10.28515625" customWidth="1" min="8" max="8"/>
+    <col width="12.42578125" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="12.42578125" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="19.140625" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10987,7 +11234,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.30416666667</v>
       </c>
       <c r="M20" t="n">
@@ -10996,7 +11243,7 @@
       <c r="N20" t="n">
         <v>-43.13229</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>46232.30208333334</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -11006,11 +11253,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.65277777778</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-22.851479</v>
@@ -11018,13 +11262,35 @@
       <c r="N21" t="n">
         <v>-43.139774</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46234.64791666667</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.42013888889</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-22.852388</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-43.139832</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>46235.41666666666</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -11041,20 +11307,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24.44140625" customWidth="1" min="1" max="1"/>
-    <col width="11.33203125" customWidth="1" min="2" max="2"/>
-    <col width="10.44140625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="12.5546875" customWidth="1" min="4" max="4"/>
-    <col width="4.109375" customWidth="1" min="5" max="5"/>
-    <col width="3.6640625" customWidth="1" min="6" max="6"/>
-    <col width="3.88671875" customWidth="1" min="7" max="7"/>
-    <col width="4.21875" customWidth="1" min="8" max="8"/>
-    <col width="4.5546875" customWidth="1" min="9" max="9"/>
-    <col width="11.5546875" customWidth="1" min="17" max="17"/>
-    <col width="18.5546875" customWidth="1" min="19" max="19"/>
+    <col width="24.42578125" customWidth="1" min="1" max="1"/>
+    <col width="11.28515625" customWidth="1" min="2" max="2"/>
+    <col width="10.42578125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="12.5703125" customWidth="1" min="4" max="4"/>
+    <col width="4.140625" customWidth="1" min="5" max="5"/>
+    <col width="3.7109375" customWidth="1" min="6" max="6"/>
+    <col width="3.85546875" customWidth="1" min="7" max="7"/>
+    <col width="4.28515625" customWidth="1" min="8" max="8"/>
+    <col width="4.5703125" customWidth="1" min="9" max="9"/>
+    <col width="11.5703125" customWidth="1" min="17" max="17"/>
+    <col width="18.5703125" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11579,7 +11845,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.30416666667</v>
       </c>
       <c r="M20" t="n">
@@ -11588,7 +11854,7 @@
       <c r="N20" t="n">
         <v>-43.135925</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>46232.29375</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -11598,11 +11864,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.65277777778</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-22.851097</v>
@@ -11610,15 +11873,37 @@
       <c r="N21" t="n">
         <v>-43.144375</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46234.64722222222</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.42013888889</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>At Anchor</t>
+      <c r="M22" t="n">
+        <v>-23.01722</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-43.06916</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>46235.41805555556</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Underway</t>
         </is>
       </c>
     </row>
@@ -11633,17 +11918,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29.33203125" customWidth="1" min="1" max="1"/>
-    <col width="3.77734375" customWidth="1" min="5" max="5"/>
-    <col width="3.33203125" customWidth="1" min="6" max="7"/>
-    <col width="2.88671875" customWidth="1" min="8" max="8"/>
-    <col width="2.33203125" customWidth="1" min="9" max="9"/>
-    <col width="13.77734375" customWidth="1" min="14" max="14"/>
-    <col width="26.109375" customWidth="1" min="17" max="17"/>
-    <col width="22.21875" customWidth="1" min="19" max="19"/>
+    <col width="29.28515625" customWidth="1" min="1" max="1"/>
+    <col width="3.7109375" customWidth="1" min="5" max="5"/>
+    <col width="3.28515625" customWidth="1" min="6" max="7"/>
+    <col width="2.85546875" customWidth="1" min="8" max="8"/>
+    <col width="2.28515625" customWidth="1" min="9" max="9"/>
+    <col width="13.7109375" customWidth="1" min="14" max="14"/>
+    <col width="26.140625" customWidth="1" min="17" max="17"/>
+    <col width="22.28515625" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12168,7 +12453,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.29930555556</v>
       </c>
       <c r="M20" t="n">
@@ -12177,7 +12462,7 @@
       <c r="N20" t="n">
         <v>-42.843231</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>46232.29583333333</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -12187,11 +12472,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.65902777778</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-25.617207</v>
@@ -12199,13 +12481,35 @@
       <c r="N21" t="n">
         <v>-42.841625</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46232.57638888889</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-25.617207</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-42.841625</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>46232.57638888889</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -12223,22 +12527,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:AI34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.5546875" customWidth="1" min="1" max="1"/>
-    <col width="18.109375" customWidth="1" min="3" max="3"/>
-    <col width="5.6640625" customWidth="1" min="4" max="4"/>
-    <col width="3.5546875" customWidth="1" min="5" max="5"/>
-    <col width="3.6640625" customWidth="1" min="6" max="6"/>
-    <col width="3.88671875" customWidth="1" min="7" max="7"/>
-    <col width="23.109375" customWidth="1" min="8" max="8"/>
-    <col width="12.44140625" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="17.6640625" customWidth="1" min="10" max="10"/>
-    <col width="21.109375" customWidth="1" min="15" max="15"/>
+    <col width="23.5703125" customWidth="1" min="1" max="1"/>
+    <col width="18.140625" customWidth="1" min="3" max="3"/>
+    <col width="5.7109375" customWidth="1" min="4" max="4"/>
+    <col width="3.5703125" customWidth="1" min="5" max="5"/>
+    <col width="3.7109375" customWidth="1" min="6" max="6"/>
+    <col width="3.85546875" customWidth="1" min="7" max="7"/>
+    <col width="23.140625" customWidth="1" min="8" max="8"/>
+    <col width="12.42578125" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="17.7109375" customWidth="1" min="10" max="10"/>
+    <col width="21.140625" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="17" max="18"/>
-    <col width="20.21875" customWidth="1" min="19" max="19"/>
-    <col width="23.77734375" customWidth="1" min="22" max="22"/>
+    <col width="20.28515625" customWidth="1" min="19" max="19"/>
+    <col width="23.7109375" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13645,7 +13949,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="n">
+      <c r="A32" s="10" t="n">
         <v>46232.29930555556</v>
       </c>
       <c r="M32" t="n">
@@ -13654,7 +13958,7 @@
       <c r="N32" t="n">
         <v>-41.102962</v>
       </c>
-      <c r="Q32" s="21" t="n">
+      <c r="Q32" s="10" t="n">
         <v>46232.29652777778</v>
       </c>
       <c r="S32" t="inlineStr">
@@ -13664,11 +13968,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="n">
+      <c r="A33" s="10" t="n">
         <v>46234.65902777778</v>
-      </c>
-      <c r="B33" t="n">
-        <v/>
       </c>
       <c r="M33" t="n">
         <v>-23.205189</v>
@@ -13676,15 +13977,37 @@
       <c r="N33" t="n">
         <v>-42.382423</v>
       </c>
-      <c r="Q33" s="21" t="n">
+      <c r="Q33" s="10" t="n">
         <v>46234.21458333333</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B34" t="n">
         <v/>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M34" t="n">
+        <v>-23.513813</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-41.065895</v>
+      </c>
+      <c r="Q34" s="21" t="n">
+        <v>46235.08680555555</v>
+      </c>
+      <c r="R34" t="n">
+        <v/>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -13700,24 +14023,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28.5546875" customWidth="1" min="1" max="1"/>
-    <col width="13.88671875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="7.44140625" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
-    <col width="12.6640625" customWidth="1" min="4" max="4"/>
-    <col width="7.109375" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="10.6640625" bestFit="1" customWidth="1" min="6" max="7"/>
-    <col width="7.109375" customWidth="1" style="3" min="8" max="8"/>
-    <col width="5.5546875" customWidth="1" min="9" max="9"/>
-    <col width="4.109375" customWidth="1" min="10" max="10"/>
-    <col width="10.6640625" bestFit="1" customWidth="1" min="11" max="14"/>
-    <col width="10.5546875" bestFit="1" customWidth="1" min="15" max="15"/>
-    <col width="5.6640625" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="28.5703125" customWidth="1" min="1" max="1"/>
+    <col width="13.85546875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="7.42578125" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
+    <col width="12.7109375" customWidth="1" min="4" max="4"/>
+    <col width="7.140625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" min="6" max="7"/>
+    <col width="7.140625" customWidth="1" style="3" min="8" max="8"/>
+    <col width="5.5703125" customWidth="1" min="9" max="9"/>
+    <col width="4.140625" customWidth="1" min="10" max="10"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" min="11" max="14"/>
+    <col width="10.5703125" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="5.7109375" bestFit="1" customWidth="1" min="16" max="16"/>
     <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="14.88671875" bestFit="1" customWidth="1" min="18" max="18"/>
-    <col width="23.33203125" customWidth="1" min="19" max="19"/>
+    <col width="14.85546875" bestFit="1" customWidth="1" min="18" max="18"/>
+    <col width="23.28515625" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15856,7 +16179,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="21" t="n">
+      <c r="A44" s="10" t="n">
         <v>46232.29930555556</v>
       </c>
       <c r="M44" t="n">
@@ -15865,7 +16188,7 @@
       <c r="N44" t="n">
         <v>-42.449718</v>
       </c>
-      <c r="Q44" s="21" t="n">
+      <c r="Q44" s="10" t="n">
         <v>46232.12222222222</v>
       </c>
       <c r="S44" t="inlineStr">
@@ -15875,11 +16198,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="21" t="n">
+      <c r="A45" s="10" t="n">
         <v>46234.65902777778</v>
-      </c>
-      <c r="B45" t="n">
-        <v/>
       </c>
       <c r="M45" t="n">
         <v>-22.881655</v>
@@ -15887,13 +16207,35 @@
       <c r="N45" t="n">
         <v>-43.117458</v>
       </c>
-      <c r="Q45" s="21" t="n">
+      <c r="Q45" s="10" t="n">
         <v>46234.65069444444</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B46" t="n">
         <v/>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="M46" t="n">
+        <v>-22.881622</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-43.117462</v>
+      </c>
+      <c r="Q46" s="21" t="n">
+        <v>46235.40486111111</v>
+      </c>
+      <c r="R46" t="n">
+        <v/>
+      </c>
+      <c r="S46" t="inlineStr">
         <is>
           <t>Moored</t>
         </is>
@@ -15910,16 +16252,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33.44140625" customWidth="1" min="1" max="1"/>
+    <col width="33.42578125" customWidth="1" min="1" max="1"/>
     <col width="4" customWidth="1" min="5" max="5"/>
-    <col width="4.109375" customWidth="1" min="6" max="6"/>
-    <col width="3.21875" customWidth="1" min="7" max="7"/>
-    <col width="4.33203125" customWidth="1" min="8" max="8"/>
-    <col width="3.77734375" customWidth="1" min="9" max="10"/>
-    <col width="11.21875" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="4.140625" customWidth="1" min="6" max="6"/>
+    <col width="3.28515625" customWidth="1" min="7" max="7"/>
+    <col width="4.28515625" customWidth="1" min="8" max="8"/>
+    <col width="3.7109375" customWidth="1" min="9" max="10"/>
+    <col width="11.28515625" bestFit="1" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16444,7 +16786,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.29930555556</v>
       </c>
       <c r="M20" t="n">
@@ -16453,7 +16795,7 @@
       <c r="N20" t="n">
         <v>-43.109585</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>44390.56527777778</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -16463,11 +16805,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.65902777778</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-22.864473</v>
@@ -16475,13 +16814,35 @@
       <c r="N21" t="n">
         <v>-43.109585</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>44390.56527777778</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-22.864473</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-43.109585</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>44390.56527777778</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Moored</t>
         </is>
@@ -16498,18 +16859,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38.77734375" customWidth="1" min="1" max="1"/>
-    <col width="6.6640625" customWidth="1" min="3" max="3"/>
-    <col width="6.33203125" customWidth="1" min="6" max="7"/>
+    <col width="38.7109375" customWidth="1" min="1" max="1"/>
+    <col width="6.7109375" customWidth="1" min="3" max="3"/>
+    <col width="6.28515625" customWidth="1" min="6" max="7"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="7.44140625" customWidth="1" min="10" max="10"/>
-    <col width="6.33203125" customWidth="1" min="11" max="11"/>
-    <col width="6.109375" customWidth="1" min="12" max="12"/>
-    <col width="12.5546875" customWidth="1" min="17" max="17"/>
-    <col width="31.6640625" customWidth="1" min="19" max="19"/>
+    <col width="7.42578125" customWidth="1" min="10" max="10"/>
+    <col width="6.28515625" customWidth="1" min="11" max="11"/>
+    <col width="6.140625" customWidth="1" min="12" max="12"/>
+    <col width="12.5703125" customWidth="1" min="17" max="17"/>
+    <col width="31.7109375" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17034,7 +17395,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.29930555556</v>
       </c>
       <c r="M20" t="n">
@@ -17043,7 +17404,7 @@
       <c r="N20" t="n">
         <v>-42.384533</v>
       </c>
-      <c r="Q20" s="21" t="n">
+      <c r="Q20" s="10" t="n">
         <v>46232.29444444444</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -17053,11 +17414,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.65902777778</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-22.848303</v>
@@ -17065,15 +17423,37 @@
       <c r="N21" t="n">
         <v>-43.133507</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46234.65277777778</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>At Anchor</t>
+      <c r="M22" t="n">
+        <v>-23.421261</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-42.944679</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>46235.39444444444</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -17088,27 +17468,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22.21875" customWidth="1" min="1" max="1"/>
-    <col width="17.109375" customWidth="1" min="2" max="2"/>
-    <col width="7.5546875" customWidth="1" style="4" min="3" max="3"/>
-    <col width="6.5546875" customWidth="1" min="4" max="4"/>
-    <col width="7.109375" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="10.6640625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="7.5546875" customWidth="1" min="7" max="7"/>
-    <col width="8.109375" customWidth="1" style="3" min="8" max="8"/>
-    <col width="7.21875" customWidth="1" min="9" max="9"/>
+    <col width="22.28515625" customWidth="1" min="1" max="1"/>
+    <col width="17.140625" customWidth="1" min="2" max="2"/>
+    <col width="7.5703125" customWidth="1" style="4" min="3" max="3"/>
+    <col width="6.5703125" customWidth="1" min="4" max="4"/>
+    <col width="7.140625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="7.5703125" customWidth="1" min="7" max="7"/>
+    <col width="8.140625" customWidth="1" style="3" min="8" max="8"/>
+    <col width="7.28515625" customWidth="1" min="9" max="9"/>
     <col width="7" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="7.33203125" customWidth="1" min="11" max="11"/>
-    <col width="7.109375" customWidth="1" min="12" max="12"/>
-    <col width="10.6640625" bestFit="1" customWidth="1" min="13" max="14"/>
-    <col width="5.88671875" customWidth="1" min="15" max="15"/>
-    <col width="6.21875" customWidth="1" min="16" max="16"/>
-    <col width="28.5546875" customWidth="1" style="9" min="17" max="17"/>
-    <col width="14.88671875" bestFit="1" customWidth="1" min="18" max="18"/>
-    <col width="17.88671875" customWidth="1" min="19" max="19"/>
+    <col width="7.28515625" customWidth="1" min="11" max="11"/>
+    <col width="7.140625" customWidth="1" min="12" max="12"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" min="13" max="14"/>
+    <col width="5.85546875" customWidth="1" min="15" max="15"/>
+    <col width="6.28515625" customWidth="1" min="16" max="16"/>
+    <col width="28.5703125" customWidth="1" style="9" min="17" max="17"/>
+    <col width="14.85546875" bestFit="1" customWidth="1" min="18" max="18"/>
+    <col width="17.85546875" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17831,7 +18211,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="n">
+      <c r="A22" s="10" t="n">
         <v>46232.29930555556</v>
       </c>
       <c r="M22" t="n">
@@ -17840,7 +18220,7 @@
       <c r="N22" t="n">
         <v>-42.446316</v>
       </c>
-      <c r="Q22" s="21" t="n">
+      <c r="Q22" s="10" t="n">
         <v>46232.28888888889</v>
       </c>
       <c r="S22" t="inlineStr">
@@ -17850,11 +18230,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="n">
+      <c r="A23" s="10" t="n">
         <v>46234.65902777778</v>
-      </c>
-      <c r="B23" t="n">
-        <v/>
       </c>
       <c r="M23" t="n">
         <v>-23.272249</v>
@@ -17862,15 +18239,37 @@
       <c r="N23" t="n">
         <v>-42.995266</v>
       </c>
-      <c r="Q23" s="21" t="n">
+      <c r="Q23" s="10" t="n">
         <v>46234.65763888889</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M24" t="n">
+        <v>-22.8946</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.212166</v>
+      </c>
+      <c r="Q24" s="21" t="n">
+        <v>46235.40486111111</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
@@ -17892,15 +18291,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="3.33203125" customWidth="1" min="5" max="7"/>
-    <col width="3.44140625" customWidth="1" min="8" max="8"/>
-    <col width="3.21875" customWidth="1" min="9" max="9"/>
-    <col width="11.21875" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="28.88671875" customWidth="1" min="19" max="19"/>
+    <col width="3.28515625" customWidth="1" min="5" max="7"/>
+    <col width="3.42578125" customWidth="1" min="8" max="8"/>
+    <col width="3.28515625" customWidth="1" min="9" max="9"/>
+    <col width="11.28515625" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="28.85546875" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18458,7 +18857,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="10" t="n">
         <v>46232.29930555556</v>
       </c>
       <c r="M21" t="n">
@@ -18467,7 +18866,7 @@
       <c r="N21" t="n">
         <v>-43.454777</v>
       </c>
-      <c r="Q21" s="21" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46232.28888888889</v>
       </c>
       <c r="S21" t="inlineStr">
@@ -18477,11 +18876,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="n">
+      <c r="A22" s="10" t="n">
         <v>46234.65902777778</v>
-      </c>
-      <c r="B22" t="n">
-        <v/>
       </c>
       <c r="M22" t="n">
         <v>-22.867237</v>
@@ -18489,13 +18885,35 @@
       <c r="N22" t="n">
         <v>-43.205769</v>
       </c>
-      <c r="Q22" s="21" t="n">
+      <c r="Q22" s="10" t="n">
         <v>46234.65763888889</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="n">
+        <v>46235.40763888889</v>
+      </c>
+      <c r="B23" t="n">
         <v/>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="M23" t="n">
+        <v>-23.313923</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-43.128742</v>
+      </c>
+      <c r="Q23" s="21" t="n">
+        <v>46235.06111111111</v>
+      </c>
+      <c r="R23" t="n">
+        <v/>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>

--- a/dados/SURVEY_CBO.xlsx
+++ b/dados/SURVEY_CBO.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.5703125" customWidth="1" min="1" max="1"/>
@@ -1118,9 +1118,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.35555555556</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.841379</v>
       </c>
@@ -1130,10 +1127,32 @@
       <c r="Q23" s="18" t="n">
         <v>46236.35416666666</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="M24" t="n">
+        <v>-22.841309</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.129326</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>46237.32777777778</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -1151,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="20.5703125" customWidth="1" min="1" max="1"/>
@@ -1753,9 +1772,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.35555555556</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-23.592419</v>
       </c>
@@ -1765,10 +1781,32 @@
       <c r="Q23" s="18" t="n">
         <v>46236.23125</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="M24" t="n">
+        <v>-23.524544</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-41.0849</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>46237.15555555555</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -1785,7 +1823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29.140625" customWidth="1" min="1" max="1"/>
@@ -2381,9 +2419,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.35902777778</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.894413</v>
       </c>
@@ -2393,10 +2428,32 @@
       <c r="Q23" s="18" t="n">
         <v>46236.35555555556</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="M24" t="n">
+        <v>-22.894377</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.201897</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>46237.32083333333</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Moored</t>
         </is>
@@ -2413,7 +2470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.42578125" customWidth="1" min="1" max="1"/>
@@ -3003,9 +3060,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.35902777778</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.836344</v>
       </c>
@@ -3015,10 +3069,32 @@
       <c r="Q23" s="18" t="n">
         <v>46236.35625</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="M24" t="n">
+        <v>-22.825138</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.091255</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>46237.32083333333</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -3035,7 +3111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3632,9 +3708,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.35902777778</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-25.160442</v>
       </c>
@@ -3644,12 +3717,34 @@
       <c r="Q23" s="18" t="n">
         <v>46236.21944444445</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Restricted Manoeuvrability</t>
+      <c r="M24" t="n">
+        <v>-22.881086</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.120499</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>46237.32708333333</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.7109375" customWidth="1" min="1" max="1"/>
@@ -4257,9 +4352,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.35902777778</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.836426</v>
       </c>
@@ -4269,12 +4361,34 @@
       <c r="Q23" s="18" t="n">
         <v>46236.35763888889</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M24" t="n">
+        <v>-22.841206</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.136509</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>46237.32430555556</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29.5703125" customWidth="1" min="1" max="1"/>
@@ -4895,9 +5009,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.35902777778</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-21.205</v>
       </c>
@@ -4907,10 +5018,32 @@
       <c r="Q23" s="18" t="n">
         <v>46234.74513888889</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="M24" t="n">
+        <v>-21.205</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-40.053333</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>46234.74513888889</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -4927,7 +5060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.140625" customWidth="1" min="1" max="1"/>
@@ -5517,9 +5650,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.35902777778</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-30.372272</v>
       </c>
@@ -5529,10 +5659,32 @@
       <c r="Q23" s="18" t="n">
         <v>44677.81111111111</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Class B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="M24" t="n">
+        <v>-30.372272</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-47.695133</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>44677.81111111111</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Class B</t>
         </is>
@@ -5549,7 +5701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -6143,9 +6295,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.35902777778</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-23.415283</v>
       </c>
@@ -6155,10 +6304,32 @@
       <c r="Q23" s="18" t="n">
         <v>46236.25208333333</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="M24" t="n">
+        <v>-22.479593</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-40.962555</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>46237.32777777778</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -6175,7 +6346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.28515625" customWidth="1" min="1" max="1"/>
@@ -6765,9 +6936,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.35902777778</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.864527</v>
       </c>
@@ -6777,10 +6945,32 @@
       <c r="Q23" s="18" t="n">
         <v>45839.57638888889</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="M24" t="n">
+        <v>-22.864527</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.111076</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>45839.57638888889</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Moored</t>
         </is>
@@ -6797,7 +6987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.85546875" customWidth="1" min="1" max="1"/>
@@ -7387,9 +7577,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.35902777778</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-24.653257</v>
       </c>
@@ -7399,10 +7586,32 @@
       <c r="Q23" s="18" t="n">
         <v>46236.21736111111</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="M24" t="n">
+        <v>-24.652611</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-42.234772</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>46237.03888888889</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -7419,7 +7628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29.28515625" customWidth="1" min="1" max="1"/>
@@ -8014,9 +8223,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.35555555556</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-25.317646</v>
       </c>
@@ -8026,12 +8232,34 @@
       <c r="Q23" s="18" t="n">
         <v>46235.79236111111</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M24" t="n">
+        <v>-22.384466</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-41.768726</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>46237.32777777778</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.28515625" customWidth="1" min="1" max="1"/>
@@ -8643,9 +8871,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.35902777778</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-24.729536</v>
       </c>
@@ -8655,12 +8880,34 @@
       <c r="Q23" s="18" t="n">
         <v>46236.12916666667</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M24" t="n">
+        <v>-21.854759</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-41.008152</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>46237.32708333333</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.140625" customWidth="1" min="1" max="1"/>
@@ -9268,9 +9515,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.34930555556</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.852297</v>
       </c>
@@ -9280,10 +9524,32 @@
       <c r="Q23" s="18" t="n">
         <v>46236.34375</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="M24" t="n">
+        <v>-22.854086</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.140125</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>46237.32152777778</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -9300,7 +9566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.42578125" customWidth="1" min="1" max="1"/>
@@ -9898,9 +10164,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.34930555556</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.847342</v>
       </c>
@@ -9910,10 +10173,32 @@
       <c r="Q23" s="18" t="n">
         <v>46236.34652777778</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.33055555556</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="M24" t="n">
+        <v>-22.846739</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.14201</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>46237.32152777778</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -9930,7 +10215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI35"/>
+  <dimension ref="A1:AI36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.5703125" customWidth="1" min="1" max="1"/>
@@ -11412,9 +11697,6 @@
       <c r="A35" s="18" t="n">
         <v>46236.35555555556</v>
       </c>
-      <c r="B35" t="n">
-        <v/>
-      </c>
       <c r="M35" t="n">
         <v>-23.565218</v>
       </c>
@@ -11424,10 +11706,32 @@
       <c r="Q35" s="18" t="n">
         <v>46236.18194444444</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B36" t="n">
         <v/>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="M36" t="n">
+        <v>-23.561159</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-41.126366</v>
+      </c>
+      <c r="Q36" s="18" t="n">
+        <v>46237.06319444445</v>
+      </c>
+      <c r="R36" t="n">
+        <v/>
+      </c>
+      <c r="S36" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -11445,7 +11749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S47"/>
+  <dimension ref="A1:S48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.5703125" customWidth="1" min="1" max="1"/>
@@ -13661,9 +13965,6 @@
       <c r="A47" s="18" t="n">
         <v>46236.35555555556</v>
       </c>
-      <c r="B47" t="n">
-        <v/>
-      </c>
       <c r="M47" t="n">
         <v>-23.6534</v>
       </c>
@@ -13673,12 +13974,34 @@
       <c r="Q47" s="18" t="n">
         <v>46235.93611111111</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="18" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B48" t="n">
         <v/>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M48" t="n">
+        <v>-24.637222</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-42.490108</v>
+      </c>
+      <c r="Q48" s="18" t="n">
+        <v>46236.76388888889</v>
+      </c>
+      <c r="R48" t="n">
+        <v/>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -13693,7 +14016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.42578125" customWidth="1" min="1" max="1"/>
@@ -14287,9 +14610,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.35555555556</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.864473</v>
       </c>
@@ -14299,10 +14619,32 @@
       <c r="Q23" s="18" t="n">
         <v>44390.56527777778</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="M24" t="n">
+        <v>-22.864473</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.109585</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>44390.56527777778</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Moored</t>
         </is>
@@ -14319,7 +14661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38.7109375" customWidth="1" min="1" max="1"/>
@@ -14915,9 +15257,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.35555555556</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-23.705391</v>
       </c>
@@ -14927,10 +15266,32 @@
       <c r="Q23" s="18" t="n">
         <v>46236.34583333333</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="M24" t="n">
+        <v>-24.041594</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-42.675713</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>46237.07291666666</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -14947,7 +15308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.28515625" customWidth="1" min="1" max="1"/>
@@ -15750,9 +16111,6 @@
       <c r="A25" s="18" t="n">
         <v>46236.35555555556</v>
       </c>
-      <c r="B25" t="n">
-        <v/>
-      </c>
       <c r="M25" t="n">
         <v>-22.881216</v>
       </c>
@@ -15762,12 +16120,34 @@
       <c r="Q25" s="18" t="n">
         <v>46236.35347222222</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B26" t="n">
         <v/>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Moored</t>
+      <c r="M26" t="n">
+        <v>-22.844997</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-43.128849</v>
+      </c>
+      <c r="Q26" s="18" t="n">
+        <v>46237.32222222222</v>
+      </c>
+      <c r="R26" t="n">
+        <v/>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -15789,7 +16169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16415,9 +16795,6 @@
       <c r="A24" s="18" t="n">
         <v>46236.35555555556</v>
       </c>
-      <c r="B24" t="n">
-        <v/>
-      </c>
       <c r="M24" t="n">
         <v>-25.530693</v>
       </c>
@@ -16427,12 +16804,34 @@
       <c r="Q24" s="18" t="n">
         <v>46236.18125</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B25" t="n">
         <v/>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M25" t="n">
+        <v>-25.536068</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-43.442936</v>
+      </c>
+      <c r="Q25" s="18" t="n">
+        <v>46237.06319444445</v>
+      </c>
+      <c r="R25" t="n">
+        <v/>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
     </row>
@@ -16447,7 +16846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5703125" customWidth="1" min="1" max="1"/>
@@ -17049,9 +17448,6 @@
       <c r="A23" s="18" t="n">
         <v>46236.35555555556</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-21.980324</v>
       </c>
@@ -17061,12 +17457,34 @@
       <c r="Q23" s="18" t="n">
         <v>46236.25833333333</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>46237.32916666667</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Restricted Manoeuvrability</t>
+      <c r="M24" t="n">
+        <v>-21.866407</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-41.015381</v>
+      </c>
+      <c r="Q24" s="18" t="n">
+        <v>46237.32430555556</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
